--- a/data/personalia/7 MN.xlsx
+++ b/data/personalia/7 MN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99EE8C20-70C6-412D-AFCD-BFBDFB2D6AD0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4761,6 +4761,9 @@
       <c r="K74" s="6">
         <v>45962</v>
       </c>
+      <c r="L74" s="6">
+        <v>46085</v>
+      </c>
       <c r="M74" s="6">
         <v>20455</v>
       </c>

--- a/data/personalia/7 MN.xlsx
+++ b/data/personalia/7 MN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99EE8C20-70C6-412D-AFCD-BFBDFB2D6AD0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E65D09-45CE-4871-99D6-B9BFA1BB58CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="295">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,6 +172,114 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
     <t>Pelaksana Informasi dan Evaluasi</t>
   </si>
   <si>
@@ -175,30 +292,45 @@
     <t>Manager STL Daop 7 Mn</t>
   </si>
   <si>
+    <t>PMP.200974.01304</t>
+  </si>
+  <si>
     <t>BURLIANI</t>
   </si>
   <si>
     <t>QC STL 7A Mn</t>
   </si>
   <si>
+    <t>PMP.060674.50111</t>
+  </si>
+  <si>
     <t>HERU EKO SULISTIAWAN</t>
   </si>
   <si>
     <t>PLT QC STL 7B Kts</t>
   </si>
   <si>
+    <t>PMP.180175.127327</t>
+  </si>
+  <si>
     <t>MUKHLISIN</t>
   </si>
   <si>
     <t>PLT QC STL 7C Kd</t>
   </si>
   <si>
+    <t>PMP.200375.65367</t>
+  </si>
+  <si>
     <t>HENDIK SUHARIYANTO</t>
   </si>
   <si>
     <t>AM Informasi dan Evaluasi Daop 7 Mn</t>
   </si>
   <si>
+    <t>PMP.170274.128044</t>
+  </si>
+  <si>
     <t>PEIHONG SINAGA</t>
   </si>
   <si>
@@ -211,6 +343,9 @@
     <t>PLT AM Perencanaan Teknis Daop 7 Mn</t>
   </si>
   <si>
+    <t>PRP.271173.126167</t>
+  </si>
+  <si>
     <t>BUDIYONO</t>
   </si>
   <si>
@@ -238,18 +373,30 @@
     <t>WS Mn</t>
   </si>
   <si>
+    <t>PRP.190177.50075</t>
+  </si>
+  <si>
+    <t>PMP.190177.67106</t>
+  </si>
+  <si>
     <t>BUDI SETIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perbaikan UPT Workshop Sintelis Madiun</t>
   </si>
   <si>
+    <t>PRP.091087.00649</t>
+  </si>
+  <si>
     <t>YOGA AKBAR DITAMA</t>
   </si>
   <si>
     <t>Supervisor Workshop Urusan Rekayasa Sintelis Madiun</t>
   </si>
   <si>
+    <t>PRP.070891.00458</t>
+  </si>
+  <si>
     <t>SUGENG BUDIARTO</t>
   </si>
   <si>
@@ -259,39 +406,66 @@
     <t>7.1 Ngw</t>
   </si>
   <si>
+    <t>PRP.060988.67806</t>
+  </si>
+  <si>
+    <t>PMP.060988.67806</t>
+  </si>
+  <si>
     <t>SUPRIYADI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.1 Ngw</t>
   </si>
   <si>
+    <t>PRP.040685.00548</t>
+  </si>
+  <si>
     <t>MAHENDRA TAMA WAHYU YULIANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.1 Ngw</t>
   </si>
   <si>
+    <t>PRP.050791.00456</t>
+  </si>
+  <si>
     <t>PEDRAHESTU NALENDRA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.1 Ngw</t>
   </si>
   <si>
+    <t>PRP.090289.00554</t>
+  </si>
+  <si>
     <t>ROHMAN QOIRUL IRAQIM</t>
   </si>
   <si>
+    <t>PRP.110992.00588</t>
+  </si>
+  <si>
     <t>ABEDNEGO GRASE SABAT</t>
   </si>
   <si>
+    <t>PRP.070101.65179</t>
+  </si>
+  <si>
     <t>HARI PURYANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.1 Ngw</t>
   </si>
   <si>
+    <t>PRP.011289.02310</t>
+  </si>
+  <si>
     <t>RENDI CANDRA IRAWAN</t>
   </si>
   <si>
+    <t>PRP.270187.00460</t>
+  </si>
+  <si>
     <t>SUDARSO</t>
   </si>
   <si>
@@ -301,42 +475,69 @@
     <t>7.2 Mn</t>
   </si>
   <si>
+    <t>PMP.300575.122282</t>
+  </si>
+  <si>
     <t>SUTANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 7.2 Mn</t>
   </si>
   <si>
+    <t>PRP.071187.126785</t>
+  </si>
+  <si>
     <t>IVANI RIZKI FADILLAH</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 7.2 Mn</t>
   </si>
   <si>
+    <t>PRP.190694.39374</t>
+  </si>
+  <si>
     <t>RIDHA PUJI PRASETYONO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.2 Mn</t>
   </si>
   <si>
+    <t>PRP.121281.00501</t>
+  </si>
+  <si>
     <t>MOHAMMAD FARIS LUTFINANTO WIBOWO</t>
   </si>
   <si>
+    <t>PRP.011000.68555</t>
+  </si>
+  <si>
     <t>SUPARNO</t>
   </si>
   <si>
+    <t>PRP.110771.116261</t>
+  </si>
+  <si>
     <t>SUYUDI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.2 Mn</t>
   </si>
   <si>
+    <t>PRP.110272.00650</t>
+  </si>
+  <si>
     <t>DANI SISWANTO HAJISAPUTRO</t>
   </si>
   <si>
+    <t>PRP.070888.00462</t>
+  </si>
+  <si>
     <t>SANDY SAPU JAGAD</t>
   </si>
   <si>
+    <t>PRP.050598.02312</t>
+  </si>
+  <si>
     <t>WAHYU TRIANA</t>
   </si>
   <si>
@@ -346,39 +547,66 @@
     <t>7.3 Nj</t>
   </si>
   <si>
+    <t>PRP.021286.126184</t>
+  </si>
+  <si>
+    <t>PMP.021286.68337</t>
+  </si>
+  <si>
     <t>YAYAN IKA PRASETYA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.3 Nj</t>
   </si>
   <si>
+    <t>PRP.161086.128689</t>
+  </si>
+  <si>
     <t>RIZAL FADILAH</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.3 Nj</t>
   </si>
   <si>
+    <t>PRP.030788.126783</t>
+  </si>
+  <si>
     <t>YULI HARIAWAN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.3 Nj</t>
   </si>
   <si>
+    <t>PRP.060785.00497</t>
+  </si>
+  <si>
     <t>BHAKTI YUDO SETYO WIDODO</t>
   </si>
   <si>
+    <t>PRP.220289.125929</t>
+  </si>
+  <si>
     <t>SUMARNO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.3 Nj</t>
   </si>
   <si>
+    <t>PRP.310790.00500</t>
+  </si>
+  <si>
     <t>BENY DWI CAHYONO</t>
   </si>
   <si>
+    <t>PRP.05051992.37735</t>
+  </si>
+  <si>
     <t>MUCHLIS JULYANSAH</t>
   </si>
   <si>
+    <t>PRP.220797.38620</t>
+  </si>
+  <si>
     <t>GENDUT ARIS SUTANTO</t>
   </si>
   <si>
@@ -388,39 +616,63 @@
     <t>7.4 Kts</t>
   </si>
   <si>
+    <t>PRP.300967.123274</t>
+  </si>
+  <si>
     <t>SLAMET ACHMADI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 7.4 Kts</t>
   </si>
   <si>
+    <t>PRP.181272.126019</t>
+  </si>
+  <si>
     <t>YUSMAN WITANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 7.4 Kts</t>
   </si>
   <si>
+    <t>PRP.270788.125884</t>
+  </si>
+  <si>
     <t>BAYU WIDODO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.4 Kts</t>
   </si>
   <si>
+    <t>PRP.260493.00616</t>
+  </si>
+  <si>
     <t>DENI RIZAJULI SETYAWAN</t>
   </si>
   <si>
+    <t>PRP.090790.02324</t>
+  </si>
+  <si>
     <t>SIKMA FERRI FEBRIANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.4 Kts</t>
   </si>
   <si>
+    <t>PRP.090393.00459</t>
+  </si>
+  <si>
     <t>FINIS ADI PUTRA</t>
   </si>
   <si>
+    <t>PRP.231089.00551</t>
+  </si>
+  <si>
     <t>HERU SISWANTO</t>
   </si>
   <si>
+    <t>PRP.251081.00557</t>
+  </si>
+  <si>
     <t>WAHYU RHOWIN PRASETYO</t>
   </si>
   <si>
@@ -430,36 +682,60 @@
     <t>7.5 Jg</t>
   </si>
   <si>
+    <t>PRP.131087.123429</t>
+  </si>
+  <si>
+    <t>PMP.131087.67807</t>
+  </si>
+  <si>
     <t>IMAM MUHAIMIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.5 Jg</t>
   </si>
   <si>
+    <t>PRP.070288.126183</t>
+  </si>
+  <si>
     <t>ANDRI HERMAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.5 Jg</t>
   </si>
   <si>
+    <t>PRP.120587.126006</t>
+  </si>
+  <si>
     <t>TRI ADI WIJAYA PURNOMO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.5 Jg</t>
   </si>
   <si>
+    <t>PRP.181096.38699</t>
+  </si>
+  <si>
     <t>PANJI DIAN SUKMANA</t>
   </si>
   <si>
+    <t>PRP.270398.02325</t>
+  </si>
+  <si>
     <t>ZAINAL ARIFIN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.5 Jg</t>
   </si>
   <si>
+    <t>PRP.011187.00647</t>
+  </si>
+  <si>
     <t>KHARIS IRAWAN</t>
   </si>
   <si>
+    <t>PRP.080397.38700</t>
+  </si>
+  <si>
     <t>ANANG SUGIYANTO</t>
   </si>
   <si>
@@ -469,36 +745,60 @@
     <t>7.6 Kd</t>
   </si>
   <si>
+    <t>PRP.090586.126007</t>
+  </si>
+  <si>
+    <t>PMP.090586.67804</t>
+  </si>
+  <si>
     <t>AGUS SUMARDJITO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.6 Kd</t>
   </si>
   <si>
+    <t>PRP.310871.126356</t>
+  </si>
+  <si>
     <t>AGUS SETIAJI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.6 Kd</t>
   </si>
   <si>
+    <t>PRP.150887.00142</t>
+  </si>
+  <si>
     <t>DARSONO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.6 Kd</t>
   </si>
   <si>
+    <t>PRP.280884.00553</t>
+  </si>
+  <si>
     <t>RIFA</t>
   </si>
   <si>
+    <t>PRP.270182.00463</t>
+  </si>
+  <si>
     <t>BAYU HANDHIKA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.6 Kd</t>
   </si>
   <si>
+    <t>PRP.010989.02313</t>
+  </si>
+  <si>
     <t>WIRANTO</t>
   </si>
   <si>
+    <t>PRP.140693.00561</t>
+  </si>
+  <si>
     <t>ENGGAR KALFIANA</t>
   </si>
   <si>
@@ -508,36 +808,57 @@
     <t>7.7 Ta</t>
   </si>
   <si>
+    <t>PRP.240889.00552</t>
+  </si>
+  <si>
     <t>YUDHA YULIANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.7 Ta</t>
   </si>
   <si>
+    <t>PRP.010788.00506</t>
+  </si>
+  <si>
     <t>HENDRA NUR ABIDIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.7 Ta</t>
   </si>
   <si>
+    <t>PRP.150488.123380</t>
+  </si>
+  <si>
     <t>REGGY EKA PRATAMA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7.7 Ta</t>
   </si>
   <si>
+    <t>PRP.040696.02327</t>
+  </si>
+  <si>
     <t>WAHYU BAGUS PRASETIYO</t>
   </si>
   <si>
+    <t>PRP.241191.02311</t>
+  </si>
+  <si>
     <t>FUJO SISWANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 7.7 Ta</t>
   </si>
   <si>
+    <t>PRP.100790.02328</t>
+  </si>
+  <si>
     <t>UGO GUMILAR</t>
   </si>
   <si>
+    <t>PRP.270402.67653</t>
+  </si>
+  <si>
     <t>AYI ROHMANI</t>
   </si>
   <si>
@@ -547,247 +868,61 @@
     <t>7.8 Bl</t>
   </si>
   <si>
+    <t>PRP.150788.123381</t>
+  </si>
+  <si>
+    <t>PMP.150786.67805</t>
+  </si>
+  <si>
     <t>KARYANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 7.8 Bl</t>
   </si>
   <si>
+    <t>PRP.210390.126784</t>
+  </si>
+  <si>
     <t>MAKHINGUDIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 7.8 Bl</t>
   </si>
   <si>
+    <t>PRP.080690.126185</t>
+  </si>
+  <si>
     <t>HERU GUSPRIYANTO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 7. 8 Bl</t>
   </si>
   <si>
+    <t>PRP.160888.00587</t>
+  </si>
+  <si>
     <t>EKA NOVA AGFI PUTERA</t>
   </si>
   <si>
-    <t>Calon Pekerja</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL 7.8 Bl</t>
   </si>
   <si>
     <t>ADI YUNIANTO</t>
   </si>
   <si>
+    <t>PRP.200689.00454</t>
+  </si>
+  <si>
     <t>PONIMAN</t>
   </si>
   <si>
+    <t>PRP.080587.00617</t>
+  </si>
+  <si>
     <t>KEPPIN SAMARITAAN</t>
   </si>
   <si>
-    <t>PMP.200974.01304</t>
-  </si>
-  <si>
-    <t>PMP.060674.50111</t>
-  </si>
-  <si>
-    <t>PMP. 180175. 127327</t>
-  </si>
-  <si>
-    <t>PRP. 200375. 128207</t>
-  </si>
-  <si>
-    <t>PMP.170274.128044</t>
-  </si>
-  <si>
-    <t>PRP.181092.128140</t>
-  </si>
-  <si>
-    <t>PRP.271173.126167</t>
-  </si>
-  <si>
-    <t>PRP.190177.50075</t>
-  </si>
-  <si>
-    <t>PRP.091087.00649</t>
-  </si>
-  <si>
-    <t>PRP.070891.00458</t>
-  </si>
-  <si>
-    <t>PRP.060988.67806</t>
-  </si>
-  <si>
-    <t>PRP.050791.00456</t>
-  </si>
-  <si>
-    <t>PRP.090289.00554</t>
-  </si>
-  <si>
-    <t>PRP.110992.00588</t>
-  </si>
-  <si>
-    <t>PRP.070101.65179</t>
-  </si>
-  <si>
-    <t>PRP.011289.02310</t>
-  </si>
-  <si>
-    <t>PRP.270187.00460</t>
-  </si>
-  <si>
-    <t>PMP.300575.122282</t>
-  </si>
-  <si>
-    <t>PRP.190694.39374</t>
-  </si>
-  <si>
-    <t>PRP.121281.00501</t>
-  </si>
-  <si>
-    <t>PRP.011000.68555</t>
-  </si>
-  <si>
-    <t>PRP.110771.116261</t>
-  </si>
-  <si>
-    <t>PRP.110272.00650</t>
-  </si>
-  <si>
-    <t>PRP.070888.00462</t>
-  </si>
-  <si>
-    <t>PRP.050598.02312</t>
-  </si>
-  <si>
-    <t>PRP.021286.126184</t>
-  </si>
-  <si>
-    <t>PRP.161086.128689</t>
-  </si>
-  <si>
-    <t>PRP.030788.126783</t>
-  </si>
-  <si>
-    <t>PRP.060785.00497</t>
-  </si>
-  <si>
-    <t>PRP.220289.125929</t>
-  </si>
-  <si>
-    <t>PRP.310790.00500</t>
-  </si>
-  <si>
-    <t>PRP.05051992.37735</t>
-  </si>
-  <si>
-    <t>PRP.220797.38620</t>
-  </si>
-  <si>
-    <t>PRP.300967.123274</t>
-  </si>
-  <si>
-    <t>PRP.270788.125884</t>
-  </si>
-  <si>
-    <t>PRP.260493.00616</t>
-  </si>
-  <si>
-    <t>PRP.090790.02324</t>
-  </si>
-  <si>
-    <t>PRP.090393.00459</t>
-  </si>
-  <si>
-    <t>PRP.231089.00551</t>
-  </si>
-  <si>
-    <t>PRP.251081.00557</t>
-  </si>
-  <si>
-    <t>PRP.131087.123429</t>
-  </si>
-  <si>
-    <t>PRP.070288.126183</t>
-  </si>
-  <si>
-    <t>PRP.120587.126006</t>
-  </si>
-  <si>
-    <t>PRP.181096.38699</t>
-  </si>
-  <si>
-    <t>PRP.011187.00647</t>
-  </si>
-  <si>
-    <t>PRP.080397.38700</t>
-  </si>
-  <si>
-    <t>PRP.090586.126007</t>
-  </si>
-  <si>
-    <t>PRP.150887.00142</t>
-  </si>
-  <si>
-    <t>PRP.280884.00553</t>
-  </si>
-  <si>
-    <t>PRP.270182.00463</t>
-  </si>
-  <si>
-    <t>PRP.140693.00561</t>
-  </si>
-  <si>
-    <t>PRP.240889.00552</t>
-  </si>
-  <si>
-    <t>PRP.150488.123380</t>
-  </si>
-  <si>
-    <t>PRP.040696.02327</t>
-  </si>
-  <si>
-    <t>PRP.241191.02311</t>
-  </si>
-  <si>
-    <t>PRP.270402.67653</t>
-  </si>
-  <si>
-    <t>PRP.150788.123381</t>
-  </si>
-  <si>
-    <t>PRP.080690.126185</t>
-  </si>
-  <si>
-    <t>PRP.200689.00454</t>
-  </si>
-  <si>
-    <t>PRP.080587.00617</t>
-  </si>
-  <si>
     <t>PRP.080802.68336</t>
-  </si>
-  <si>
-    <t>PMP.180175.127327</t>
-  </si>
-  <si>
-    <t>PMP.200375.65367</t>
-  </si>
-  <si>
-    <t>PMP.190177.67106</t>
-  </si>
-  <si>
-    <t>PMP.060988.67806</t>
-  </si>
-  <si>
-    <t>PMP.021286.68337</t>
-  </si>
-  <si>
-    <t>PMP.131087.67807</t>
-  </si>
-  <si>
-    <t>PMP.090586.67804</t>
-  </si>
-  <si>
-    <t>PMP.150786.67805</t>
   </si>
 </sst>
 </file>
@@ -858,9 +993,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -869,8 +1001,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1174,30 +1309,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T91"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1353,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1228,19 +1362,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1249,7 +1383,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1261,10 +1395,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>40989</v>
@@ -1275,13 +1409,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>47</v>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45627</v>
       </c>
       <c r="I2" s="2">
@@ -1290,36 +1424,31 @@
       <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>34274</v>
       </c>
-      <c r="L2" s="6">
-        <v>27292</v>
-      </c>
-      <c r="M2" s="6">
+      <c r="L2" s="5">
+        <v>28320</v>
+      </c>
+      <c r="M2" s="5">
         <v>47757</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="Q2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="5">
         <v>46816</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="R2" s="6">
-        <v>46816</v>
-      </c>
-      <c r="S2" s="3"/>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2">
         <v>44877</v>
@@ -1330,13 +1459,13 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>49</v>
+      <c r="F3" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45945</v>
       </c>
       <c r="I3" s="2">
@@ -1345,36 +1474,31 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>35217</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>27186</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>47665</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="O3" s="6">
-        <v>46697</v>
-      </c>
-      <c r="P3" s="3"/>
       <c r="Q3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="R3" s="6">
+        <v>87</v>
+      </c>
+      <c r="R3" s="5">
         <v>47370</v>
       </c>
-      <c r="S3" s="3"/>
+      <c r="S3" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2">
         <v>45881</v>
@@ -1385,13 +1509,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>51</v>
+      <c r="F4" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45915</v>
       </c>
       <c r="I4" s="2">
@@ -1400,35 +1524,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35490</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>27412</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>47880</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45693</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="R4" s="6">
+        <v>90</v>
+      </c>
+      <c r="R4" s="5">
         <v>47370</v>
       </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2">
         <v>44886</v>
@@ -1439,14 +1559,14 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>53</v>
+      <c r="F5" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
-        <v>46060</v>
+      <c r="H5" s="5">
+        <v>45627</v>
       </c>
       <c r="I5" s="2">
         <v>11</v>
@@ -1454,35 +1574,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L5" s="5">
         <v>27473</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>47939</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45747</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="R5" s="6">
+        <v>93</v>
+      </c>
+      <c r="R5" s="5">
         <v>47008</v>
       </c>
-      <c r="S5" s="3"/>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2">
         <v>45874</v>
@@ -1493,14 +1609,14 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>55</v>
+      <c r="F6" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
-        <v>44927</v>
+      <c r="H6" s="5">
+        <v>44270</v>
       </c>
       <c r="I6" s="2">
         <v>9</v>
@@ -1508,34 +1624,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>35490</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>27077</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>47543</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O6" s="6">
-        <v>45747</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="R6" s="6">
+        <v>96</v>
+      </c>
+      <c r="R6" s="5">
         <v>47265</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2">
         <v>69499</v>
@@ -1546,13 +1659,13 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>57</v>
+      <c r="F7" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>45371</v>
       </c>
       <c r="I7" s="2">
@@ -1561,29 +1674,22 @@
       <c r="J7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>42562</v>
       </c>
-      <c r="L7" s="6">
-        <v>33895</v>
-      </c>
-      <c r="M7" s="6">
+      <c r="L7" s="5">
+        <v>31314</v>
+      </c>
+      <c r="M7" s="5">
         <v>54363</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="O7" s="6">
-        <v>45747</v>
-      </c>
-      <c r="S7" s="3"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2">
         <v>48736</v>
@@ -1594,13 +1700,13 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>59</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>45945</v>
       </c>
       <c r="I8" s="2">
@@ -1609,29 +1715,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L8" s="5">
         <v>26995</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>47453</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="O8" s="6">
+        <v>101</v>
+      </c>
+      <c r="O8" s="5">
         <v>47005</v>
       </c>
-      <c r="S8" s="3"/>
+      <c r="P8" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>45832</v>
@@ -1642,13 +1750,13 @@
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
+      <c r="F9" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>45809</v>
       </c>
       <c r="I9" s="2">
@@ -1657,22 +1765,22 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="K9" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L9" s="5">
         <v>28366</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>48823</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>51152</v>
@@ -1683,14 +1791,14 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>62</v>
+      <c r="F10" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+      <c r="H10" s="5">
+        <v>40909</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
@@ -1698,23 +1806,22 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>39600</v>
       </c>
-      <c r="L10" s="6">
-        <v>27243</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="L10" s="5">
+        <v>27068</v>
+      </c>
+      <c r="M10" s="5">
         <v>47727</v>
       </c>
-      <c r="S10" s="3"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2">
         <v>47980</v>
@@ -1725,14 +1832,14 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>62</v>
+      <c r="F11" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+      <c r="H11" s="5">
+        <v>40808</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
@@ -1740,23 +1847,22 @@
       <c r="J11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L11" s="5">
         <v>26251</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>46722</v>
       </c>
-      <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2">
         <v>69577</v>
@@ -1767,14 +1873,14 @@
       <c r="E12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>65</v>
+      <c r="F12" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="6">
-        <v>44927</v>
+      <c r="H12" s="5">
+        <v>43602</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -1782,23 +1888,22 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L12" s="5">
         <v>32000</v>
       </c>
-      <c r="M12" s="6">
-        <v>52475</v>
-      </c>
-      <c r="S12" s="3"/>
+      <c r="M12" s="5">
+        <v>52566</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2">
         <v>46481</v>
@@ -1809,13 +1914,13 @@
       <c r="E13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>67</v>
+      <c r="F13" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="6">
+        <v>110</v>
+      </c>
+      <c r="H13" s="5">
         <v>45992</v>
       </c>
       <c r="I13" s="2">
@@ -1824,35 +1929,40 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L13" s="5">
         <v>28144</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>48611</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" s="6">
+        <v>111</v>
+      </c>
+      <c r="O13" s="5">
         <v>46697</v>
       </c>
+      <c r="P13" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q13" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R13" s="6">
+        <v>112</v>
+      </c>
+      <c r="R13" s="5">
         <v>47097</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="S13" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>62096</v>
@@ -1863,14 +1973,14 @@
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>70</v>
+      <c r="F14" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44927</v>
+        <v>110</v>
+      </c>
+      <c r="H14" s="5">
+        <v>44659</v>
       </c>
       <c r="I14" s="2">
         <v>8</v>
@@ -1878,29 +1988,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
-        <v>40917</v>
-      </c>
-      <c r="L14" s="6">
-        <v>32030</v>
-      </c>
-      <c r="M14" s="6">
-        <v>52505</v>
+      <c r="K14" s="5">
+        <v>41153</v>
+      </c>
+      <c r="L14" s="5">
+        <v>32059</v>
+      </c>
+      <c r="M14" s="5">
+        <v>52536</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="O14" s="6">
+        <v>115</v>
+      </c>
+      <c r="O14" s="5">
         <v>46433</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="P14" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="C15" s="2">
         <v>55024</v>
@@ -1911,13 +2023,13 @@
       <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>72</v>
+      <c r="F15" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="6">
+        <v>110</v>
+      </c>
+      <c r="H15" s="5">
         <v>45976</v>
       </c>
       <c r="I15" s="2">
@@ -1926,29 +2038,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>40163</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>33427</v>
       </c>
-      <c r="M15" s="6">
-        <v>53905</v>
+      <c r="M15" s="5">
+        <v>53936</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="O15" s="6">
+        <v>118</v>
+      </c>
+      <c r="O15" s="5">
         <v>46837</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="P15" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2">
         <v>53085</v>
@@ -1959,13 +2073,13 @@
       <c r="E16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>74</v>
+      <c r="F16" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="6">
+        <v>121</v>
+      </c>
+      <c r="H16" s="5">
         <v>45580</v>
       </c>
       <c r="I16" s="2">
@@ -1974,35 +2088,40 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L16" s="6">
-        <v>32303</v>
-      </c>
-      <c r="M16" s="6">
-        <v>52779</v>
+      <c r="K16" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L16" s="5">
+        <v>31433</v>
+      </c>
+      <c r="M16" s="5">
+        <v>52871</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="6">
+        <v>122</v>
+      </c>
+      <c r="O16" s="5">
         <v>47203</v>
       </c>
+      <c r="P16" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="R16" s="6">
+        <v>123</v>
+      </c>
+      <c r="R16" s="5">
         <v>47114</v>
       </c>
-      <c r="S16" s="3"/>
+      <c r="S16" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2">
         <v>49735</v>
@@ -2013,14 +2132,14 @@
       <c r="E17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>77</v>
+      <c r="F17" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H17" s="5">
+        <v>44287</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
@@ -2028,22 +2147,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="K17" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L17" s="5">
         <v>31143</v>
       </c>
-      <c r="M17" s="6">
-        <v>51622</v>
+      <c r="M17" s="5">
+        <v>51683</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O17" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2">
         <v>56104</v>
@@ -2054,13 +2182,13 @@
       <c r="E18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>79</v>
+      <c r="F18" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="6">
+        <v>121</v>
+      </c>
+      <c r="H18" s="5">
         <v>45976</v>
       </c>
       <c r="I18" s="2">
@@ -2069,29 +2197,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>40163</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>33365</v>
       </c>
-      <c r="M18" s="6">
-        <v>53844</v>
+      <c r="M18" s="5">
+        <v>53905</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="O18" s="6">
+        <v>129</v>
+      </c>
+      <c r="O18" s="5">
         <v>46837</v>
       </c>
-      <c r="S18" s="3"/>
+      <c r="P18" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2">
         <v>59512</v>
@@ -2102,14 +2232,14 @@
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
+      <c r="F19" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H19" s="5">
+        <v>42005</v>
       </c>
       <c r="I19" s="2">
         <v>5</v>
@@ -2117,29 +2247,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="K19" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L19" s="5">
         <v>32753</v>
       </c>
-      <c r="M19" s="6">
-        <v>53236</v>
+      <c r="M19" s="5">
+        <v>53022</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O19" s="6">
+        <v>132</v>
+      </c>
+      <c r="O19" s="5">
         <v>46881</v>
       </c>
-      <c r="S19" s="3"/>
+      <c r="P19" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2">
         <v>61433</v>
@@ -2150,14 +2282,14 @@
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>81</v>
+      <c r="F20" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H20" s="5">
+        <v>44872</v>
       </c>
       <c r="I20" s="2">
         <v>5</v>
@@ -2165,29 +2297,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="K20" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L20" s="5">
         <v>33917</v>
       </c>
-      <c r="M20" s="6">
-        <v>54393</v>
+      <c r="M20" s="5">
+        <v>54332</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="O20" s="6">
+        <v>134</v>
+      </c>
+      <c r="O20" s="5">
         <v>46881</v>
       </c>
-      <c r="S20" s="3"/>
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2">
         <v>75256</v>
@@ -2198,13 +2332,13 @@
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>81</v>
+      <c r="F21" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="6">
+        <v>121</v>
+      </c>
+      <c r="H21" s="5">
         <v>45658</v>
       </c>
       <c r="I21" s="2">
@@ -2213,29 +2347,31 @@
       <c r="J21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>44958</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>36898</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>57377</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="O21" s="6">
+        <v>136</v>
+      </c>
+      <c r="O21" s="5">
         <v>47005</v>
       </c>
-      <c r="S21" s="3"/>
+      <c r="P21" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2">
         <v>69572</v>
@@ -2246,14 +2382,14 @@
       <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>85</v>
+      <c r="F22" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H22" s="5">
+        <v>43325</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
@@ -2261,29 +2397,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="K22" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L22" s="5">
         <v>32520</v>
       </c>
-      <c r="M22" s="6">
-        <v>52994</v>
+      <c r="M22" s="5">
+        <v>53328</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="O22" s="6">
+        <v>139</v>
+      </c>
+      <c r="O22" s="5">
         <v>46211</v>
       </c>
-      <c r="S22" s="3"/>
+      <c r="P22" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="C23" s="2">
         <v>53055</v>
@@ -2294,14 +2432,14 @@
       <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>85</v>
+      <c r="F23" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H23" s="5">
+        <v>42005</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -2309,29 +2447,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="K23" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L23" s="5">
         <v>31804</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>52263</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="O23" s="6">
+        <v>141</v>
+      </c>
+      <c r="O23" s="5">
         <v>46881</v>
       </c>
-      <c r="S23" s="3"/>
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2">
         <v>43395</v>
@@ -2342,13 +2482,13 @@
       <c r="E24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>88</v>
+      <c r="F24" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="6">
+        <v>144</v>
+      </c>
+      <c r="H24" s="5">
         <v>45962</v>
       </c>
       <c r="I24" s="2">
@@ -2357,34 +2497,31 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>35217</v>
       </c>
-      <c r="L24" s="6">
-        <v>27544</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="L24" s="5">
+        <v>27536</v>
+      </c>
+      <c r="M24" s="5">
         <v>48000</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="O24" s="6">
+      <c r="Q24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R24" s="5">
         <v>46916</v>
       </c>
-      <c r="Q24" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="R24" s="6">
-        <v>46916</v>
+      <c r="S24" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2">
         <v>50083</v>
@@ -2395,13 +2532,13 @@
       <c r="E25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>91</v>
+      <c r="F25" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="6">
+        <v>144</v>
+      </c>
+      <c r="H25" s="5">
         <v>45103</v>
       </c>
       <c r="I25" s="2">
@@ -2410,23 +2547,31 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L25" s="6">
-        <v>31969</v>
-      </c>
-      <c r="M25" s="6">
-        <v>52444</v>
-      </c>
-      <c r="S25" s="3"/>
+      <c r="K25" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L25" s="5">
+        <v>31608</v>
+      </c>
+      <c r="M25" s="5">
+        <v>52566</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="O25" s="5">
+        <v>47203</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2">
         <v>70536</v>
@@ -2437,13 +2582,13 @@
       <c r="E26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>93</v>
+      <c r="F26" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="6">
+        <v>144</v>
+      </c>
+      <c r="H26" s="5">
         <v>45627</v>
       </c>
       <c r="I26" s="2">
@@ -2452,29 +2597,31 @@
       <c r="J26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L26" s="6">
-        <v>34504</v>
-      </c>
-      <c r="M26" s="6">
+      <c r="K26" s="5">
+        <v>42646</v>
+      </c>
+      <c r="L26" s="5">
+        <v>33927</v>
+      </c>
+      <c r="M26" s="5">
         <v>54970</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="O26" s="6">
+        <v>151</v>
+      </c>
+      <c r="O26" s="5">
         <v>47370</v>
       </c>
-      <c r="S26" s="3"/>
+      <c r="P26" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C27" s="2">
         <v>56052</v>
@@ -2485,14 +2632,14 @@
       <c r="E27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>95</v>
+      <c r="F27" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H27" s="5">
+        <v>44872</v>
       </c>
       <c r="I27" s="2">
         <v>5</v>
@@ -2500,29 +2647,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>40163</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>29932</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>50406</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="O27" s="6">
+        <v>154</v>
+      </c>
+      <c r="O27" s="5">
         <v>46837</v>
       </c>
-      <c r="S27" s="3"/>
+      <c r="P27" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2">
         <v>75375</v>
@@ -2533,13 +2682,13 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>95</v>
+      <c r="F28" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="6">
+        <v>144</v>
+      </c>
+      <c r="H28" s="5">
         <v>45976</v>
       </c>
       <c r="I28" s="2">
@@ -2548,29 +2697,31 @@
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>44958</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>36800</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>57285</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="O28" s="6">
+        <v>156</v>
+      </c>
+      <c r="O28" s="5">
         <v>47111</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="C29" s="2">
         <v>59599</v>
@@ -2581,14 +2732,14 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>95</v>
+      <c r="F29" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H29" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H29" s="5">
+        <v>42005</v>
       </c>
       <c r="I29" s="2">
         <v>5</v>
@@ -2596,29 +2747,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>40575</v>
       </c>
-      <c r="L29" s="6">
-        <v>26125</v>
-      </c>
-      <c r="M29" s="6">
+      <c r="L29" s="5">
+        <v>26244</v>
+      </c>
+      <c r="M29" s="5">
         <v>46600</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O29" s="6">
+        <v>158</v>
+      </c>
+      <c r="O29" s="5">
         <v>46937</v>
       </c>
-      <c r="S29" s="3"/>
+      <c r="P29" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C30" s="2">
         <v>43384</v>
@@ -2629,14 +2782,14 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>99</v>
+      <c r="F30" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H30" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H30" s="5">
+        <v>42005</v>
       </c>
       <c r="I30" s="2">
         <v>5</v>
@@ -2644,29 +2797,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>35217</v>
       </c>
-      <c r="L30" s="6">
-        <v>26340</v>
-      </c>
-      <c r="M30" s="6">
+      <c r="L30" s="5">
+        <v>26605</v>
+      </c>
+      <c r="M30" s="5">
         <v>46813</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="O30" s="6">
+        <v>161</v>
+      </c>
+      <c r="O30" s="5">
         <v>46837</v>
       </c>
-      <c r="S30" s="3"/>
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2">
         <v>53083</v>
@@ -2677,14 +2832,14 @@
       <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>99</v>
+      <c r="F31" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H31" s="5">
+        <v>44682</v>
       </c>
       <c r="I31" s="2">
         <v>5</v>
@@ -2692,29 +2847,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L31" s="6">
-        <v>32332</v>
-      </c>
-      <c r="M31" s="6">
-        <v>52810</v>
+      <c r="K31" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L31" s="5">
+        <v>32362</v>
+      </c>
+      <c r="M31" s="5">
+        <v>52841</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="O31" s="6">
+        <v>163</v>
+      </c>
+      <c r="O31" s="5">
         <v>46837</v>
       </c>
-      <c r="S31" s="3"/>
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2">
         <v>69593</v>
@@ -2725,14 +2882,14 @@
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>99</v>
+      <c r="F32" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H32" s="5">
+        <v>43800</v>
       </c>
       <c r="I32" s="2">
         <v>5</v>
@@ -2740,28 +2897,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L32" s="6">
+      <c r="K32" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L32" s="5">
         <v>35920</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>56401</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="O32" s="6">
+        <v>165</v>
+      </c>
+      <c r="O32" s="5">
         <v>46211</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="C33" s="2">
         <v>49916</v>
@@ -2772,13 +2932,13 @@
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>103</v>
+      <c r="F33" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="6">
+        <v>168</v>
+      </c>
+      <c r="H33" s="5">
         <v>45580</v>
       </c>
       <c r="I33" s="2">
@@ -2787,35 +2947,40 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L33" s="6">
+      <c r="K33" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L33" s="5">
         <v>31455</v>
       </c>
-      <c r="M33" s="6">
-        <v>51926</v>
+      <c r="M33" s="5">
+        <v>52232</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="6">
+        <v>169</v>
+      </c>
+      <c r="O33" s="5">
         <v>46937</v>
       </c>
+      <c r="P33" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q33" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="R33" s="6">
+        <v>170</v>
+      </c>
+      <c r="R33" s="5">
         <v>47114</v>
       </c>
-      <c r="S33" s="3"/>
+      <c r="S33" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2">
         <v>53052</v>
@@ -2826,13 +2991,13 @@
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>106</v>
+      <c r="F34" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="6">
+        <v>168</v>
+      </c>
+      <c r="H34" s="5">
         <v>45580</v>
       </c>
       <c r="I34" s="2">
@@ -2841,35 +3006,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="K34" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L34" s="5">
         <v>31701</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>52171</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="O34" s="6">
+        <v>173</v>
+      </c>
+      <c r="O34" s="5">
         <v>47285</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="R34" s="6">
-        <v>47285</v>
-      </c>
-      <c r="S34" s="3"/>
+      <c r="P34" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="35" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2">
         <v>50216</v>
@@ -2880,14 +3041,14 @@
       <c r="E35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>108</v>
+      <c r="F35" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="6">
-        <v>44927</v>
+        <v>168</v>
+      </c>
+      <c r="H35" s="5">
+        <v>44820</v>
       </c>
       <c r="I35" s="2">
         <v>7</v>
@@ -2895,29 +3056,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L35" s="6">
-        <v>32209</v>
-      </c>
-      <c r="M35" s="6">
-        <v>52688</v>
+      <c r="K35" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L35" s="5">
+        <v>32327</v>
+      </c>
+      <c r="M35" s="5">
+        <v>52810</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="O35" s="6">
+        <v>176</v>
+      </c>
+      <c r="O35" s="5">
         <v>47203</v>
       </c>
-      <c r="S35" s="3"/>
+      <c r="P35" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2">
         <v>56051</v>
@@ -2928,14 +3091,14 @@
       <c r="E36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>110</v>
+      <c r="F36" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H36" s="6">
-        <v>44927</v>
+        <v>168</v>
+      </c>
+      <c r="H36" s="5">
+        <v>44287</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -2943,29 +3106,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>40163</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="5">
         <v>31205</v>
       </c>
-      <c r="M36" s="6">
-        <v>51683</v>
+      <c r="M36" s="5">
+        <v>51714</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="O36" s="6">
+        <v>179</v>
+      </c>
+      <c r="O36" s="5">
         <v>46881</v>
       </c>
-      <c r="S36" s="3"/>
+      <c r="P36" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2">
         <v>50380</v>
@@ -2976,13 +3141,13 @@
       <c r="E37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>110</v>
+      <c r="F37" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="6">
+        <v>168</v>
+      </c>
+      <c r="H37" s="5">
         <v>45853</v>
       </c>
       <c r="I37" s="2">
@@ -2991,29 +3156,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L37" s="6">
-        <v>32561</v>
-      </c>
-      <c r="M37" s="6">
+      <c r="K37" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L37" s="5">
+        <v>32804</v>
+      </c>
+      <c r="M37" s="5">
         <v>53022</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="O37" s="6">
+        <v>181</v>
+      </c>
+      <c r="O37" s="5">
         <v>47005</v>
       </c>
-      <c r="S37" s="3"/>
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2">
         <v>56088</v>
@@ -3024,14 +3191,14 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>113</v>
+      <c r="F38" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" s="6">
-        <v>44927</v>
+        <v>168</v>
+      </c>
+      <c r="H38" s="5">
+        <v>43089</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>
@@ -3039,28 +3206,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <v>40163</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>33085</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>53540</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O38" s="6">
+        <v>184</v>
+      </c>
+      <c r="O38" s="5">
         <v>47114</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="C39" s="2">
         <v>69584</v>
@@ -3071,14 +3241,14 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>113</v>
+      <c r="F39" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="6">
-        <v>44927</v>
+        <v>168</v>
+      </c>
+      <c r="H39" s="5">
+        <v>43325</v>
       </c>
       <c r="I39" s="2">
         <v>5</v>
@@ -3086,29 +3256,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="K39" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L39" s="5">
         <v>33729</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>54210</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O39" s="6">
+        <v>186</v>
+      </c>
+      <c r="O39" s="5">
         <v>46263</v>
       </c>
-      <c r="S39" s="3"/>
+      <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="C40" s="2">
         <v>69581</v>
@@ -3119,13 +3291,13 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>113</v>
+      <c r="F40" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" s="6">
+        <v>168</v>
+      </c>
+      <c r="H40" s="5">
         <v>45139</v>
       </c>
       <c r="I40" s="2">
@@ -3134,29 +3306,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L40" s="6">
+      <c r="K40" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L40" s="5">
         <v>35633</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>56097</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O40" s="6">
+        <v>188</v>
+      </c>
+      <c r="O40" s="5">
         <v>46407</v>
       </c>
-      <c r="S40" s="3"/>
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="41" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="C41" s="2">
         <v>43406</v>
@@ -3167,13 +3341,13 @@
       <c r="E41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>117</v>
+      <c r="F41" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H41" s="6">
+        <v>191</v>
+      </c>
+      <c r="H41" s="5">
         <v>45962</v>
       </c>
       <c r="I41" s="2">
@@ -3182,29 +3356,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="K41" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L41" s="5">
         <v>28033</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>48488</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="O41" s="6">
+        <v>192</v>
+      </c>
+      <c r="O41" s="5">
         <v>46837</v>
       </c>
-      <c r="S41" s="3"/>
+      <c r="P41" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="C42" s="2">
         <v>40415</v>
@@ -3215,14 +3391,14 @@
       <c r="E42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>120</v>
+      <c r="F42" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H42" s="6">
-        <v>44927</v>
+        <v>191</v>
+      </c>
+      <c r="H42" s="5">
+        <v>44287</v>
       </c>
       <c r="I42" s="2">
         <v>8</v>
@@ -3230,23 +3406,31 @@
       <c r="J42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="6">
-        <v>33249</v>
-      </c>
-      <c r="L42" s="6">
+      <c r="K42" s="5">
+        <v>33543</v>
+      </c>
+      <c r="L42" s="5">
         <v>26651</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="5">
         <v>47119</v>
       </c>
-      <c r="S42" s="3"/>
+      <c r="N42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O42" s="5">
+        <v>46965</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="C43" s="2">
         <v>56366</v>
@@ -3257,13 +3441,13 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>122</v>
+      <c r="F43" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H43" s="6">
+        <v>191</v>
+      </c>
+      <c r="H43" s="5">
         <v>45103</v>
       </c>
       <c r="I43" s="2">
@@ -3272,29 +3456,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L43" s="6">
-        <v>32321</v>
-      </c>
-      <c r="M43" s="6">
-        <v>52779</v>
+      <c r="K43" s="5">
+        <v>40163</v>
+      </c>
+      <c r="L43" s="5">
+        <v>32351</v>
+      </c>
+      <c r="M43" s="5">
+        <v>52810</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O43" s="6">
+        <v>198</v>
+      </c>
+      <c r="O43" s="5">
         <v>46937</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="P43" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="C44" s="2">
         <v>61450</v>
@@ -3305,14 +3491,14 @@
       <c r="E44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>124</v>
+      <c r="F44" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="6">
-        <v>44927</v>
+        <v>191</v>
+      </c>
+      <c r="H44" s="5">
+        <v>44075</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
@@ -3320,28 +3506,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L44" s="6">
+      <c r="K44" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L44" s="5">
         <v>34085</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>54544</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="O44" s="6">
+        <v>201</v>
+      </c>
+      <c r="O44" s="5">
         <v>46881</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="C45" s="2">
         <v>69597</v>
@@ -3352,13 +3541,13 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>124</v>
+      <c r="F45" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H45" s="6">
+        <v>191</v>
+      </c>
+      <c r="H45" s="5">
         <v>45139</v>
       </c>
       <c r="I45" s="2">
@@ -3367,29 +3556,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L45" s="6">
+      <c r="K45" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L45" s="5">
         <v>33123</v>
       </c>
-      <c r="M45" s="6">
-        <v>53601</v>
+      <c r="M45" s="5">
+        <v>53540</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="O45" s="6">
+        <v>203</v>
+      </c>
+      <c r="O45" s="5">
         <v>46208</v>
       </c>
-      <c r="S45" s="3"/>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2">
         <v>61444</v>
@@ -3400,13 +3591,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>127</v>
+      <c r="F46" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="6">
+        <v>191</v>
+      </c>
+      <c r="H46" s="5">
         <v>44958</v>
       </c>
       <c r="I46" s="2">
@@ -3415,29 +3606,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L46" s="6">
+      <c r="K46" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L46" s="5">
         <v>34215</v>
       </c>
-      <c r="M46" s="6">
-        <v>54697</v>
+      <c r="M46" s="5">
+        <v>54514</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="O46" s="6">
+        <v>206</v>
+      </c>
+      <c r="O46" s="5">
         <v>47203</v>
       </c>
-      <c r="S46" s="3"/>
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2">
         <v>53140</v>
@@ -3448,13 +3641,13 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>127</v>
+      <c r="F47" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H47" s="6">
+        <v>168</v>
+      </c>
+      <c r="H47" s="5">
         <v>45853</v>
       </c>
       <c r="I47" s="2">
@@ -3463,29 +3656,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L47" s="6">
+      <c r="K47" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L47" s="5">
         <v>32804</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>53267</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="O47" s="6">
+        <v>208</v>
+      </c>
+      <c r="O47" s="5">
         <v>46937</v>
       </c>
-      <c r="S47" s="3"/>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2">
         <v>59597</v>
@@ -3496,14 +3691,14 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>127</v>
+      <c r="F48" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H48" s="6">
-        <v>44927</v>
+        <v>191</v>
+      </c>
+      <c r="H48" s="5">
+        <v>44287</v>
       </c>
       <c r="I48" s="2">
         <v>5</v>
@@ -3511,29 +3706,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L48" s="6">
+      <c r="K48" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L48" s="5">
         <v>29884</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>50345</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="O48" s="6">
+        <v>210</v>
+      </c>
+      <c r="O48" s="5">
         <v>47265</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="P48" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>130</v>
+        <v>211</v>
       </c>
       <c r="C49" s="2">
         <v>50070</v>
@@ -3544,13 +3741,13 @@
       <c r="E49" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>131</v>
+      <c r="F49" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H49" s="6">
+        <v>213</v>
+      </c>
+      <c r="H49" s="5">
         <v>45580</v>
       </c>
       <c r="I49" s="2">
@@ -3559,35 +3756,40 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L49" s="6">
+      <c r="K49" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L49" s="5">
         <v>32063</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>52536</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="O49" s="6">
+        <v>214</v>
+      </c>
+      <c r="O49" s="5">
         <v>46937</v>
       </c>
+      <c r="P49" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q49" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="R49" s="6">
+        <v>215</v>
+      </c>
+      <c r="R49" s="5">
         <v>47114</v>
       </c>
-      <c r="S49" s="3"/>
+      <c r="S49" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="50" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2">
         <v>50130</v>
@@ -3598,13 +3800,13 @@
       <c r="E50" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>134</v>
+      <c r="F50" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H50" s="6">
+        <v>213</v>
+      </c>
+      <c r="H50" s="5">
         <v>45580</v>
       </c>
       <c r="I50" s="2">
@@ -3613,29 +3815,31 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L50" s="6">
+      <c r="K50" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L50" s="5">
         <v>32326</v>
       </c>
-      <c r="M50" s="6">
-        <v>52810</v>
+      <c r="M50" s="5">
+        <v>52657</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O50" s="6">
+        <v>218</v>
+      </c>
+      <c r="O50" s="5">
         <v>47114</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="P50" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="51" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2">
         <v>53060</v>
@@ -3646,14 +3850,14 @@
       <c r="E51" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>136</v>
+      <c r="F51" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H51" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H51" s="5">
+        <v>44820</v>
       </c>
       <c r="I51" s="2">
         <v>7</v>
@@ -3661,30 +3865,31 @@
       <c r="J51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L51" s="6">
+      <c r="K51" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L51" s="5">
         <v>32116</v>
       </c>
-      <c r="M51" s="6">
-        <v>52597</v>
+      <c r="M51" s="5">
+        <v>52383</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="O51" s="6">
+        <v>221</v>
+      </c>
+      <c r="O51" s="5">
         <v>46937</v>
       </c>
-      <c r="P51" s="3"/>
-      <c r="S51" s="3"/>
+      <c r="P51" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="C52" s="2">
         <v>70796</v>
@@ -3695,14 +3900,14 @@
       <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>138</v>
+      <c r="F52" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H52" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H52" s="5">
+        <v>44075</v>
       </c>
       <c r="I52" s="2">
         <v>5</v>
@@ -3710,30 +3915,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="5">
         <v>42725</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="5">
         <v>35356</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="5">
         <v>55824</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O52" s="6">
+        <v>224</v>
+      </c>
+      <c r="O52" s="5">
         <v>46407</v>
       </c>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
+      <c r="P52" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2">
         <v>68922</v>
@@ -3744,14 +3950,14 @@
       <c r="E53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>138</v>
+      <c r="F53" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H53" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H53" s="5">
+        <v>44075</v>
       </c>
       <c r="I53" s="2">
         <v>5</v>
@@ -3759,24 +3965,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L53" s="6">
+      <c r="K53" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L53" s="5">
         <v>35881</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>56340</v>
       </c>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="N53" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="O53" s="5">
+        <v>46208</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="C54" s="2">
         <v>59513</v>
@@ -3787,14 +4000,14 @@
       <c r="E54" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>141</v>
+      <c r="F54" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H54" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H54" s="5">
+        <v>44287</v>
       </c>
       <c r="I54" s="2">
         <v>5</v>
@@ -3802,30 +4015,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L54" s="6">
+      <c r="K54" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L54" s="5">
         <v>31788</v>
       </c>
-      <c r="M54" s="6">
-        <v>52263</v>
+      <c r="M54" s="5">
+        <v>52566</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="O54" s="6">
+        <v>229</v>
+      </c>
+      <c r="O54" s="5">
         <v>47203</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="P54" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="C55" s="2">
         <v>71380</v>
@@ -3836,13 +4050,13 @@
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>141</v>
+      <c r="F55" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H55" s="6">
+        <v>213</v>
+      </c>
+      <c r="H55" s="5">
         <v>44958</v>
       </c>
       <c r="I55" s="2">
@@ -3851,30 +4065,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L55" s="6">
-        <v>35645</v>
-      </c>
-      <c r="M55" s="6">
-        <v>56128</v>
+      <c r="K55" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L55" s="5">
+        <v>35497</v>
+      </c>
+      <c r="M55" s="5">
+        <v>55975</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="O55" s="6">
+        <v>231</v>
+      </c>
+      <c r="O55" s="5">
         <v>46407</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="C56" s="2">
         <v>49842</v>
@@ -3885,13 +4100,13 @@
       <c r="E56" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>144</v>
+      <c r="F56" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H56" s="6">
+        <v>234</v>
+      </c>
+      <c r="H56" s="5">
         <v>45580</v>
       </c>
       <c r="I56" s="2">
@@ -3900,36 +4115,40 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L56" s="6">
+      <c r="K56" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L56" s="5">
         <v>31660</v>
       </c>
-      <c r="M56" s="6">
-        <v>52140</v>
+      <c r="M56" s="5">
+        <v>52018</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O56" s="6">
+        <v>235</v>
+      </c>
+      <c r="O56" s="5">
         <v>46937</v>
       </c>
-      <c r="P56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q56" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="R56" s="6">
+        <v>236</v>
+      </c>
+      <c r="R56" s="5">
         <v>47114</v>
       </c>
-      <c r="S56" s="3"/>
+      <c r="S56" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="57" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2">
         <v>59598</v>
@@ -3940,14 +4159,14 @@
       <c r="E57" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>147</v>
+      <c r="F57" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H57" s="6">
-        <v>44927</v>
+        <v>234</v>
+      </c>
+      <c r="H57" s="5">
+        <v>43753</v>
       </c>
       <c r="I57" s="2">
         <v>7</v>
@@ -3955,24 +4174,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L57" s="6">
+      <c r="K57" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L57" s="5">
         <v>26176</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>46631</v>
       </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="N57" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="O57" s="5">
+        <v>46965</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="58" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="C58" s="2">
         <v>53065</v>
@@ -3983,13 +4209,13 @@
       <c r="E58" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>149</v>
+      <c r="F58" s="7" t="s">
+        <v>241</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H58" s="6">
+        <v>234</v>
+      </c>
+      <c r="H58" s="5">
         <v>45103</v>
       </c>
       <c r="I58" s="2">
@@ -3998,30 +4224,31 @@
       <c r="J58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L58" s="6">
+      <c r="K58" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L58" s="5">
         <v>32004</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>52475</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O58" s="6">
+        <v>242</v>
+      </c>
+      <c r="O58" s="5">
         <v>46881</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="P58" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="C59" s="2">
         <v>59601</v>
@@ -4032,14 +4259,14 @@
       <c r="E59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>151</v>
+      <c r="F59" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H59" s="6">
-        <v>44927</v>
+        <v>234</v>
+      </c>
+      <c r="H59" s="5">
+        <v>44287</v>
       </c>
       <c r="I59" s="2">
         <v>5</v>
@@ -4047,30 +4274,31 @@
       <c r="J59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L59" s="6">
+      <c r="K59" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L59" s="5">
         <v>30922</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>51380</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O59" s="6">
+        <v>245</v>
+      </c>
+      <c r="O59" s="5">
         <v>46965</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="P59" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2">
         <v>59514</v>
@@ -4081,14 +4309,14 @@
       <c r="E60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>151</v>
+      <c r="F60" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H60" s="6">
-        <v>44927</v>
+        <v>234</v>
+      </c>
+      <c r="H60" s="5">
+        <v>44596</v>
       </c>
       <c r="I60" s="2">
         <v>5</v>
@@ -4096,30 +4324,31 @@
       <c r="J60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L60" s="6">
+      <c r="K60" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L60" s="5">
         <v>29978</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>50437</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="O60" s="6">
+        <v>247</v>
+      </c>
+      <c r="O60" s="5">
         <v>47265</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="P60" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="C61" s="2">
         <v>69602</v>
@@ -4130,14 +4359,14 @@
       <c r="E61" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>154</v>
+      <c r="F61" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H61" s="6">
-        <v>44927</v>
+        <v>234</v>
+      </c>
+      <c r="H61" s="5">
+        <v>43325</v>
       </c>
       <c r="I61" s="2">
         <v>5</v>
@@ -4145,24 +4374,31 @@
       <c r="J61" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L61" s="6">
+      <c r="K61" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L61" s="5">
         <v>32517</v>
       </c>
-      <c r="M61" s="6">
-        <v>52994</v>
-      </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="M61" s="5">
+        <v>53236</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O61" s="5">
+        <v>46208</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
       <c r="C62" s="2">
         <v>61457</v>
@@ -4173,13 +4409,13 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>154</v>
+      <c r="F62" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H62" s="6">
+        <v>234</v>
+      </c>
+      <c r="H62" s="5">
         <v>44958</v>
       </c>
       <c r="I62" s="2">
@@ -4188,30 +4424,31 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L62" s="6">
+      <c r="K62" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L62" s="5">
         <v>34134</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>54605</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="O62" s="6">
+        <v>252</v>
+      </c>
+      <c r="O62" s="5">
         <v>47265</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="C63" s="2">
         <v>53127</v>
@@ -4222,13 +4459,13 @@
       <c r="E63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>157</v>
+      <c r="F63" s="7" t="s">
+        <v>254</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H63" s="6">
+        <v>255</v>
+      </c>
+      <c r="H63" s="5">
         <v>45962</v>
       </c>
       <c r="I63" s="2">
@@ -4237,30 +4474,31 @@
       <c r="J63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K63" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L63" s="6">
+      <c r="K63" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L63" s="5">
         <v>32744</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>53206</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O63" s="6">
+        <v>256</v>
+      </c>
+      <c r="O63" s="5">
         <v>47285</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="64" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>159</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2">
         <v>53078</v>
@@ -4271,14 +4509,14 @@
       <c r="E64" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>160</v>
+      <c r="F64" s="7" t="s">
+        <v>258</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H64" s="6">
-        <v>44927</v>
+        <v>255</v>
+      </c>
+      <c r="H64" s="5">
+        <v>44287</v>
       </c>
       <c r="I64" s="2">
         <v>7</v>
@@ -4286,24 +4524,31 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L64" s="6">
+      <c r="K64" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L64" s="5">
         <v>32149</v>
       </c>
-      <c r="M64" s="6">
-        <v>52628</v>
-      </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="M64" s="5">
+        <v>52810</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O64" s="5">
+        <v>46937</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="C65" s="2">
         <v>50172</v>
@@ -4314,14 +4559,14 @@
       <c r="E65" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>162</v>
+      <c r="F65" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H65" s="6">
-        <v>44927</v>
+        <v>255</v>
+      </c>
+      <c r="H65" s="5">
+        <v>44075</v>
       </c>
       <c r="I65" s="2">
         <v>7</v>
@@ -4329,30 +4574,31 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L65" s="6">
+      <c r="K65" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L65" s="5">
         <v>32248</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>52718</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O65" s="6">
+        <v>262</v>
+      </c>
+      <c r="O65" s="5">
         <v>46937</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="P65" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="C66" s="2">
         <v>69562</v>
@@ -4363,14 +4609,14 @@
       <c r="E66" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>164</v>
+      <c r="F66" s="7" t="s">
+        <v>264</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H66" s="6">
-        <v>44927</v>
+        <v>255</v>
+      </c>
+      <c r="H66" s="5">
+        <v>43325</v>
       </c>
       <c r="I66" s="2">
         <v>5</v>
@@ -4378,30 +4624,31 @@
       <c r="J66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L66" s="6">
+      <c r="K66" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L66" s="5">
         <v>35161</v>
       </c>
-      <c r="M66" s="6">
-        <v>55640</v>
+      <c r="M66" s="5">
+        <v>55701</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="O66" s="6">
+        <v>265</v>
+      </c>
+      <c r="O66" s="5">
         <v>46208</v>
       </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="P66" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="C67" s="2">
         <v>68939</v>
@@ -4412,14 +4659,14 @@
       <c r="E67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>164</v>
+      <c r="F67" s="7" t="s">
+        <v>264</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H67" s="6">
-        <v>44927</v>
+        <v>255</v>
+      </c>
+      <c r="H67" s="5">
+        <v>43325</v>
       </c>
       <c r="I67" s="2">
         <v>5</v>
@@ -4427,47 +4674,48 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L67" s="6">
+      <c r="K67" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L67" s="5">
         <v>33566</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>54027</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O67" s="6">
+        <v>267</v>
+      </c>
+      <c r="O67" s="5">
         <v>46208</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="P67" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="C68" s="2">
         <v>68928</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>167</v>
+      <c r="F68" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H68" s="8">
+        <v>255</v>
+      </c>
+      <c r="H68" s="5">
         <v>44958</v>
       </c>
       <c r="I68" s="2">
@@ -4476,41 +4724,48 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L68" s="6">
+      <c r="K68" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L68" s="5">
         <v>33153</v>
       </c>
-      <c r="M68" s="6">
-        <v>53632</v>
-      </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="M68" s="5">
+        <v>53540</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="O68" s="5">
+        <v>46208</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>168</v>
+        <v>271</v>
       </c>
       <c r="C69" s="2">
         <v>75378</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>167</v>
+      <c r="F69" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H69" s="8">
+        <v>255</v>
+      </c>
+      <c r="H69" s="5">
         <v>45658</v>
       </c>
       <c r="I69" s="2">
@@ -4519,47 +4774,48 @@
       <c r="J69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <v>44958</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>37373</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>57831</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O69" s="6">
+        <v>272</v>
+      </c>
+      <c r="O69" s="5">
         <v>47114</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
+      <c r="P69" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2">
         <v>49872</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>170</v>
+      <c r="F70" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H70" s="6">
+        <v>275</v>
+      </c>
+      <c r="H70" s="5">
         <v>45103</v>
       </c>
       <c r="I70" s="2">
@@ -4568,54 +4824,58 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L70" s="6">
-        <v>31608</v>
-      </c>
-      <c r="M70" s="6">
+      <c r="K70" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L70" s="5">
+        <v>32303</v>
+      </c>
+      <c r="M70" s="5">
         <v>52079</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="O70" s="6">
+        <v>276</v>
+      </c>
+      <c r="O70" s="5">
         <v>46937</v>
       </c>
-      <c r="P70" s="3"/>
+      <c r="P70" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q70" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="R70" s="6">
+        <v>277</v>
+      </c>
+      <c r="R70" s="5">
         <v>47114</v>
       </c>
-      <c r="S70" s="3"/>
+      <c r="S70" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="71" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="C71" s="2">
         <v>50538</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>173</v>
+      <c r="F71" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H71" s="8">
-        <v>44927</v>
+        <v>275</v>
+      </c>
+      <c r="H71" s="5">
+        <v>44287</v>
       </c>
       <c r="I71" s="2">
         <v>7</v>
@@ -4623,42 +4883,49 @@
       <c r="J71" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L71" s="6">
+      <c r="K71" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L71" s="5">
         <v>32953</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>53418</v>
       </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
+      <c r="N71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="O71" s="5">
+        <v>47203</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="72" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="C72" s="2">
         <v>53917</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>175</v>
+      <c r="F72" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H72" s="8">
-        <v>44927</v>
+        <v>275</v>
+      </c>
+      <c r="H72" s="5">
+        <v>44635</v>
       </c>
       <c r="I72" s="2">
         <v>7</v>
@@ -4666,48 +4933,49 @@
       <c r="J72" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <v>39814</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>33091</v>
       </c>
-      <c r="M72" s="6">
-        <v>53571</v>
+      <c r="M72" s="5">
+        <v>53509</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O72" s="6">
+        <v>283</v>
+      </c>
+      <c r="O72" s="5">
         <v>46937</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
+      <c r="P72" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C73" s="2">
         <v>56303</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>177</v>
+      <c r="F73" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H73" s="6">
-        <v>44927</v>
+        <v>275</v>
+      </c>
+      <c r="H73" s="5">
+        <v>42583</v>
       </c>
       <c r="I73" s="2">
         <v>5</v>
@@ -4715,41 +4983,48 @@
       <c r="J73" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>40163</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>32371</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="5">
         <v>52841</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="N73" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="O73" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2">
         <v>78109</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>180</v>
+        <v>65</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H74" s="6">
+        <v>275</v>
+      </c>
+      <c r="H74" s="5">
         <v>45962</v>
       </c>
       <c r="I74" s="2">
@@ -4758,42 +5033,40 @@
       <c r="J74" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="5">
         <v>45962</v>
       </c>
-      <c r="L74" s="6">
-        <v>46085</v>
-      </c>
-      <c r="M74" s="6">
-        <v>20455</v>
-      </c>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
+      <c r="L74" s="5">
+        <v>36468</v>
+      </c>
+      <c r="M74" s="5">
+        <v>56949</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>181</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2">
         <v>56261</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>180</v>
+      <c r="F75" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H75" s="8">
-        <v>44927</v>
+        <v>275</v>
+      </c>
+      <c r="H75" s="5">
+        <v>43259</v>
       </c>
       <c r="I75" s="2">
         <v>5</v>
@@ -4801,48 +5074,49 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="5">
         <v>40163</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="5">
         <v>32679</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>53144</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O75" s="6">
+        <v>290</v>
+      </c>
+      <c r="O75" s="5">
         <v>46837</v>
       </c>
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
+      <c r="P75" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="C76" s="2">
         <v>59725</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>180</v>
+      <c r="F76" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H76" s="8">
-        <v>44927</v>
+        <v>275</v>
+      </c>
+      <c r="H76" s="5">
+        <v>42583</v>
       </c>
       <c r="I76" s="2">
         <v>5</v>
@@ -4850,47 +5124,48 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L76" s="6">
+      <c r="K76" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L76" s="5">
         <v>31994</v>
       </c>
-      <c r="M76" s="6">
-        <v>52475</v>
+      <c r="M76" s="5">
+        <v>52383</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O76" s="6">
+        <v>292</v>
+      </c>
+      <c r="O76" s="5">
         <v>46881</v>
       </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="P76" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>183</v>
+        <v>293</v>
       </c>
       <c r="C77" s="2">
         <v>75246</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>180</v>
+      <c r="F77" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H77" s="8">
+        <v>275</v>
+      </c>
+      <c r="H77" s="5">
         <v>45658</v>
       </c>
       <c r="I77" s="2">
@@ -4899,113 +5174,190 @@
       <c r="J77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="5">
         <v>44927</v>
       </c>
-      <c r="L77" s="6">
+      <c r="L77" s="5">
         <v>37568</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="5">
         <v>58045</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O77" s="6">
+        <v>294</v>
+      </c>
+      <c r="O77" s="5">
         <v>47114</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="H78" s="8"/>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="H79" s="8"/>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="H80" s="8"/>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
-    </row>
-    <row r="81" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H81" s="8"/>
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H82" s="8"/>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P84" s="3"/>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H86" s="8"/>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H87" s="8"/>
-      <c r="P87" s="3"/>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H88" s="8"/>
-      <c r="P88" s="3"/>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P89" s="3"/>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="H90" s="8"/>
-      <c r="P90" s="3"/>
-      <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="8:19" x14ac:dyDescent="0.45">
-      <c r="P91" s="3"/>
-      <c r="S91" s="3"/>
-    </row>
+      <c r="P77" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="81" x14ac:dyDescent="0.45"/>
+    <row r="82" x14ac:dyDescent="0.45"/>
+    <row r="83" x14ac:dyDescent="0.45"/>
+    <row r="84" x14ac:dyDescent="0.45"/>
+    <row r="85" x14ac:dyDescent="0.45"/>
+    <row r="86" x14ac:dyDescent="0.45"/>
+    <row r="87" x14ac:dyDescent="0.45"/>
+    <row r="88" x14ac:dyDescent="0.45"/>
+    <row r="89" x14ac:dyDescent="0.45"/>
+    <row r="90" x14ac:dyDescent="0.45"/>
+    <row r="91" x14ac:dyDescent="0.45"/>
+    <row r="92" x14ac:dyDescent="0.45"/>
+    <row r="93" x14ac:dyDescent="0.45"/>
+    <row r="94" x14ac:dyDescent="0.45"/>
+    <row r="95" x14ac:dyDescent="0.45"/>
+    <row r="96" x14ac:dyDescent="0.45"/>
+    <row r="97" x14ac:dyDescent="0.45"/>
+    <row r="98" x14ac:dyDescent="0.45"/>
+    <row r="99" x14ac:dyDescent="0.45"/>
+    <row r="100" x14ac:dyDescent="0.45"/>
+    <row r="101" x14ac:dyDescent="0.45"/>
+    <row r="102" x14ac:dyDescent="0.45"/>
+    <row r="103" x14ac:dyDescent="0.45"/>
+    <row r="104" x14ac:dyDescent="0.45"/>
+    <row r="105" x14ac:dyDescent="0.45"/>
+    <row r="106" x14ac:dyDescent="0.45"/>
+    <row r="107" x14ac:dyDescent="0.45"/>
+    <row r="108" x14ac:dyDescent="0.45"/>
+    <row r="109" x14ac:dyDescent="0.45"/>
+    <row r="110" x14ac:dyDescent="0.45"/>
+    <row r="111" x14ac:dyDescent="0.45"/>
+    <row r="112" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T116" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D993</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J993</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I993</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5015,130 +5367,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
